--- a/public/documents/pieces-defense/RF-pertes-biere-mousse.xlsx
+++ b/public/documents/pieces-defense/RF-pertes-biere-mousse.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Biere pression tiree" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Freinte chiffree" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biere servie par produit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Freinte par exercice" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,12 +467,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,193 +492,295 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mousse, purge, fond de fut et nettoyage des lignes : volume tire mais jamais servi. Rendement-fut courant ~95 % (≈5 % mini) ; litterature CHR 5-20 %.</t>
+          <t>Biere pression servie par produit et par exercice, puis freinte technique (sur-versement/collerette, mousse &amp; tirage, nettoyage des lignes + purge + fond). Freinte retenue 20 % du fut (moyenne sectorielle, Modern Restaurant Management), au-dessus des 15 % du service.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Article (part biere du fut)</t>
+          <t>Article (part biere)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Quantite (3 ans)</t>
+          <t>Part biere (cl)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Volume biere (L)</t>
+          <t>2022-23 qte</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2022-23 L</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2023-24 qte</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2023-24 L</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2024-25 qte</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2024-25 L</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Total qte</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Total L</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Monaco (25 cl)</t>
+          <t>pression</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>18</v>
+        <v>902</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>670</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>662</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2234</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Panaché (25 cl)</t>
+          <t>Pinte</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>244</v>
+        <v>50</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>61</v>
+        <v>282</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>308</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>877</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Picon bière (25 cl)</t>
+          <t>Picon bière</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>252</v>
+        <v>25</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63</v>
+        <v>129</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Pinte (50 cl)</t>
+          <t>Panaché</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>590</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>295</v>
+        <v>147</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Pinte Picon (50 cl)</t>
+          <t>Pinte Picon</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>48</v>
+        <v>37</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>pression (25 cl)</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1564</v>
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>391</v>
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Monaco (25 cl)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Panaché (25 cl)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Picon bière (25 cl)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Pinte (50 cl)</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>286</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Pinte Picon (50 cl)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>pression (25 cl)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>670</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL biere pression</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>4130</v>
-      </c>
-      <c r="C17" s="7" t="n">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL biere servie</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="7" t="n">
+        <v>1497</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>454</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>416</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1324</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>423</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>4132</v>
+      </c>
+      <c r="J11" s="7" t="n">
         <v>1293</v>
       </c>
     </row>
@@ -686,12 +795,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -704,70 +817,145 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mousse, purge, fond de fut et nettoyage des lignes : volume tire mais jamais servi. Rendement-fut courant ~95 % (≈5 % mini) ; litterature CHR 5-20 %.</t>
+          <t>Biere pression servie par produit et par exercice, puis freinte technique (sur-versement/collerette, mousse &amp; tirage, nettoyage des lignes + purge + fond). Freinte retenue 20 % du fut (moyenne sectorielle, Modern Restaurant Management), au-dessus des 15 % du service.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Hypothese de freinte</t>
+          <t>Periode</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Taux</t>
+          <t>Biere servie (L)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Litres perdus (3 ans)</t>
+          <t>Sur-versement/collerette 7% (L)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Mousse &amp; tirage 8% (L)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Nettoyage+purge+fond 5% (L)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Freinte totale (L)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Taux % du fut</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Borne basse (rendement-fut ~95 %)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>5 %</t>
-        </is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>454</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>65</v>
+        <v>40</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>RETENU (mode CHR)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>10 %</t>
-        </is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>416</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>129</v>
+        <v>36</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Borne haute CHR</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>18 %</t>
-        </is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>423</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>233</v>
+        <v>37</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>113</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>129</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>323</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/public/documents/pieces-defense/RF-pertes-biere-mousse.xlsx
+++ b/public/documents/pieces-defense/RF-pertes-biere-mousse.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Biere servie par produit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Biere servie par article" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Freinte par exercice" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -467,19 +467,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,257 +500,280 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Article (part biere)</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Contenance verre (cl)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>Part biere (cl)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2022-23 qte</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2022-23 L</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>2022-23 L biere</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>2023-24 qte</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2023-24 L</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>2023-24 L biere</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>2024-25 qte</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2024-25 L</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>2024-25 L biere</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Total qte</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Total L</t>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Total L biere</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>pression</t>
+          <t>Pression 25 cl</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>25</v>
       </c>
       <c r="C5" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>902</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="E5" s="5" t="n">
         <v>225</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>670</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>168</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <v>662</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>166</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>2234</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5" s="5" t="n">
         <v>558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Pinte</t>
+          <t>Pression 50 cl (pinte)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>50</v>
       </c>
       <c r="C6" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>282</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="E6" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>286</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <v>308</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>154</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>877</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Picon bière</t>
+          <t>Panaché 25 cl</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
         <v>25</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>129</v>
+        <v>12.5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>382</v>
+        <v>12</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>96</v>
+        <v>346</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Panaché</t>
+          <t>Picon bière 25 cl</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>25</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>346</v>
+        <v>28</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>87</v>
+        <v>382</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Pinte Picon</t>
+          <t>Picon bière 50 cl</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
         <v>50</v>
       </c>
       <c r="C9" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>18</v>
-      </c>
       <c r="E9" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="G9" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="I9" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="J9" s="5" t="n">
         <v>162</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>81</v>
+      <c r="K9" s="5" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Monaco 25 cl</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>25</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>14</v>
-      </c>
       <c r="G10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="H10" s="5" t="n">
-        <v>18</v>
-      </c>
       <c r="I10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>32</v>
+      <c r="K10" s="5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -759,29 +783,30 @@
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr"/>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="7" t="n">
         <v>1497</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>454</v>
-      </c>
       <c r="E11" s="7" t="n">
+        <v>432</v>
+      </c>
+      <c r="F11" s="7" t="n">
         <v>1312</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>416</v>
-      </c>
       <c r="G11" s="7" t="n">
+        <v>391</v>
+      </c>
+      <c r="H11" s="7" t="n">
         <v>1324</v>
       </c>
-      <c r="H11" s="7" t="n">
-        <v>423</v>
-      </c>
       <c r="I11" s="7" t="n">
+        <v>396</v>
+      </c>
+      <c r="J11" s="7" t="n">
         <v>4132</v>
       </c>
-      <c r="J11" s="7" t="n">
-        <v>1293</v>
+      <c r="K11" s="7" t="n">
+        <v>1219</v>
       </c>
     </row>
   </sheetData>
@@ -865,19 +890,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>20</v>
@@ -890,19 +915,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>20</v>
@@ -915,19 +940,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>20</v>
@@ -940,19 +965,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>1293</v>
+        <v>1219</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>20</v>

--- a/public/documents/pieces-defense/RF-pertes-biere-mousse.xlsx
+++ b/public/documents/pieces-defense/RF-pertes-biere-mousse.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Biere servie par article" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Freinte par exercice" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sources &amp; conventions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -986,4 +987,284 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pertes de biere pression - freinte technique du fut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Biere pression servie par produit et par exercice, puis freinte technique (sur-versement/collerette, mousse &amp; tirage, nettoyage des lignes + purge + fond). Freinte retenue 20 % du fut (moyenne sectorielle, Modern Restaurant Management), au-dessus des 15 % du service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Detail / Source (lien)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CONVENTIONS DE PART BIERE</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Pression 25 cl / 50 cl</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Part biere = contenance (biere pure) : 25 cl / 50 cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Panache 25 cl</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Part biere 12,5 cl (moitie biere + limonade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Monaco 25 cl</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Part biere 12,5 cl (biere + limonade + trait de grenadine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Picon biere 25 cl</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Part biere 23 cl (2 cl de Picon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Picon biere 50 cl</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Part biere 46 cl (4 cl de Picon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Distinction 25/50 cl</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Lue sur l'article de caisse (insensible au prix, qui varie par periode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TAUX DE FREINTE (% du fut tire)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Sur-versement / collerette</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>7 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Mousse &amp; tirage (temperature, pression, debut/fond de fut)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Nettoyage des lignes + purge + fond de fut</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Total freinte retenue</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>20 % du fut = 305 L sur 3 ans</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Fourchette documentee</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>5 % a 25 %, moyenne ~20 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Retranche par le service (fisc)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>15 % (Proposition p. 51)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Modern Restaurant Management (moyenne 20 %/fut ; mousse = 25 % de biere)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>https://modernrestaurantmanagement.com/seven-wasteful-sins-how-youre-losing-profits-on-draft-beer-sales/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Bar-i (fourchette 5-25 % ; moussage &gt; 10 %)</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>https://blog.bar-i.com/what-is-the-normal-waste-level-for-draft-beer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Brewers Association - Draught Beer Quality Manual (nettoyage lignes / 14 jours)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.brewersassociation.org/educational-publications/draught-beer-quality-manual/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Le Bihan Boissons - CHR France (~10 %/fut)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>https://lebihanboissons.com/tirage-pression-comment-choisir-ses-futs-et-eviter-la-perte-mousse-stockage-service/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>JDC - CHR France (~15 %)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jdc.fr/blog/reduire-gaspillage-de-biere-bar</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/documents/pieces-defense/RF-pertes-biere-mousse.xlsx
+++ b/public/documents/pieces-defense/RF-pertes-biere-mousse.xlsx
@@ -860,7 +860,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Sur-versement/collerette 7% (L)</t>
+          <t>Collerette/mousse au service 7% (L)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Sur-versement / collerette</t>
+          <t>Collerette et mousse au service</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
